--- a/data/nzd0088/nzd0088.xlsx
+++ b/data/nzd0088/nzd0088.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F322"/>
+  <dimension ref="A1:F323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8162,6 +8162,30 @@
       <c r="F322" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="C323" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="D323" t="n">
+        <v>344.99</v>
+      </c>
+      <c r="E323" t="n">
+        <v>347.15</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B331"/>
+  <dimension ref="A1:B332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11489,6 +11513,16 @@
       </c>
       <c r="B331" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -11657,28 +11691,28 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06244293721750433</v>
+        <v>0.05935081729621949</v>
       </c>
       <c r="J2" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K2" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01068206688433271</v>
+        <v>0.009692795806562571</v>
       </c>
       <c r="M2" t="n">
-        <v>3.285002724739352</v>
+        <v>3.290201636479604</v>
       </c>
       <c r="N2" t="n">
-        <v>19.04543666625226</v>
+        <v>19.05716682916535</v>
       </c>
       <c r="O2" t="n">
-        <v>4.364107774362621</v>
+        <v>4.365451503471932</v>
       </c>
       <c r="P2" t="n">
-        <v>349.4329896821648</v>
+        <v>349.4668878327511</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11735,28 +11769,28 @@
         <v>0.0854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1866647948296478</v>
+        <v>0.1829797403714115</v>
       </c>
       <c r="J3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06889466156510782</v>
+        <v>0.06657001783447236</v>
       </c>
       <c r="M3" t="n">
-        <v>3.575462323077675</v>
+        <v>3.582314618464931</v>
       </c>
       <c r="N3" t="n">
-        <v>24.83600732334952</v>
+        <v>24.85954301181477</v>
       </c>
       <c r="O3" t="n">
-        <v>4.983573750166593</v>
+        <v>4.985934517401404</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8339381616149</v>
+        <v>345.8743365077735</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11813,28 +11847,28 @@
         <v>0.0801</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1915491266724862</v>
+        <v>0.1863897767196638</v>
       </c>
       <c r="J4" t="n">
+        <v>322</v>
+      </c>
+      <c r="K4" t="n">
         <v>321</v>
       </c>
-      <c r="K4" t="n">
-        <v>320</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1112095049293416</v>
+        <v>0.1053939713399813</v>
       </c>
       <c r="M4" t="n">
-        <v>2.982699935979413</v>
+        <v>3.00166212371714</v>
       </c>
       <c r="N4" t="n">
-        <v>15.47581588616331</v>
+        <v>15.62529944255065</v>
       </c>
       <c r="O4" t="n">
-        <v>3.933931352497564</v>
+        <v>3.952884951848542</v>
       </c>
       <c r="P4" t="n">
-        <v>347.8651731043991</v>
+        <v>347.9217755981462</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11891,28 +11925,28 @@
         <v>0.0842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.234130279729737</v>
+        <v>0.2273571426876638</v>
       </c>
       <c r="J5" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K5" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1257933427727194</v>
+        <v>0.1184588242367517</v>
       </c>
       <c r="M5" t="n">
-        <v>3.438525169565808</v>
+        <v>3.461844933212573</v>
       </c>
       <c r="N5" t="n">
-        <v>20.09163678670763</v>
+        <v>20.36931590056272</v>
       </c>
       <c r="O5" t="n">
-        <v>4.482369550439548</v>
+        <v>4.513237851095677</v>
       </c>
       <c r="P5" t="n">
-        <v>351.4015331607361</v>
+        <v>351.4757853971431</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11950,7 +11984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F322"/>
+  <dimension ref="A1:F323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22253,6 +22287,38 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-35.55039130798053,174.4710537608129</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-35.551122596139564,174.47123376431588</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-35.55181333685448,174.4715899290335</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-35.55244215112031,174.47207150677977</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0088/nzd0088.xlsx
+++ b/data/nzd0088/nzd0088.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F323"/>
+  <dimension ref="A1:F325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8184,6 +8184,54 @@
         <v>347.15</v>
       </c>
       <c r="F323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>344.93</v>
+      </c>
+      <c r="C324" t="n">
+        <v>343.87</v>
+      </c>
+      <c r="D324" t="n">
+        <v>344.62</v>
+      </c>
+      <c r="E324" t="n">
+        <v>345.37</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>345.93</v>
+      </c>
+      <c r="C325" t="n">
+        <v>345.14</v>
+      </c>
+      <c r="D325" t="n">
+        <v>346.19</v>
+      </c>
+      <c r="E325" t="n">
+        <v>346.55</v>
+      </c>
+      <c r="F325" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8200,7 +8248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B332"/>
+  <dimension ref="A1:B334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11523,6 +11571,26 @@
       </c>
       <c r="B332" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -11691,28 +11759,28 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05935081729621949</v>
+        <v>0.05219822636717207</v>
       </c>
       <c r="J2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009692795806562571</v>
+        <v>0.007543723973118088</v>
       </c>
       <c r="M2" t="n">
-        <v>3.290201636479604</v>
+        <v>3.305943092651673</v>
       </c>
       <c r="N2" t="n">
-        <v>19.05716682916535</v>
+        <v>19.13274330340893</v>
       </c>
       <c r="O2" t="n">
-        <v>4.365451503471932</v>
+        <v>4.374099141927275</v>
       </c>
       <c r="P2" t="n">
-        <v>349.4668878327511</v>
+        <v>349.5455360052099</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11769,28 +11837,28 @@
         <v>0.0854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1829797403714115</v>
+        <v>0.1749965697154225</v>
       </c>
       <c r="J3" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K3" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06657001783447236</v>
+        <v>0.06149127107419583</v>
       </c>
       <c r="M3" t="n">
-        <v>3.582314618464931</v>
+        <v>3.599606217010469</v>
       </c>
       <c r="N3" t="n">
-        <v>24.85954301181477</v>
+        <v>24.947330231003</v>
       </c>
       <c r="O3" t="n">
-        <v>4.985934517401404</v>
+        <v>4.994730246069651</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8743365077735</v>
+        <v>345.962117082313</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11847,28 +11915,28 @@
         <v>0.0801</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1863897767196638</v>
+        <v>0.1768310509803756</v>
       </c>
       <c r="J4" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K4" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1053939713399813</v>
+        <v>0.09518428536757451</v>
       </c>
       <c r="M4" t="n">
-        <v>3.00166212371714</v>
+        <v>3.035233796549456</v>
       </c>
       <c r="N4" t="n">
-        <v>15.62529944255065</v>
+        <v>15.8752459641329</v>
       </c>
       <c r="O4" t="n">
-        <v>3.952884951848542</v>
+        <v>3.984375228832357</v>
       </c>
       <c r="P4" t="n">
-        <v>347.9217755981462</v>
+        <v>348.0269591950798</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11925,28 +11993,28 @@
         <v>0.0842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2273571426876638</v>
+        <v>0.212590175076789</v>
       </c>
       <c r="J5" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K5" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1184588242367517</v>
+        <v>0.102759947338792</v>
       </c>
       <c r="M5" t="n">
-        <v>3.461844933212573</v>
+        <v>3.514658000953649</v>
       </c>
       <c r="N5" t="n">
-        <v>20.36931590056272</v>
+        <v>21.06256783140669</v>
       </c>
       <c r="O5" t="n">
-        <v>4.513237851095677</v>
+        <v>4.589397327689845</v>
       </c>
       <c r="P5" t="n">
-        <v>351.4757853971431</v>
+        <v>351.6381621840969</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11984,7 +12052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F323"/>
+  <dimension ref="A1:F325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22319,6 +22387,70 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-35.55039400854791,174.47103901451095</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-35.551126046578965,174.47122075410218</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-35.55181486089847,174.47158629859356</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-35.55245040594504,174.47205466923432</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-35.550392037331015,174.4710497782351</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-35.55112251266118,174.4712340790791</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-35.55180839400838,174.4716017034324</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-35.55244493364575,174.47206583120305</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
